--- a/4-偏倚风险评价（数据表）.xlsx
+++ b/4-偏倚风险评价（数据表）.xlsx
@@ -2049,7 +2049,7 @@
       </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
-          <t>无。冻结表1b.1反向问法记PN（个体在分配前已按既有班级成建制识别），等价于官方1b.1为Y/PY，按须知§三"分配前已完成个体识别／招募→低风险"；1b.4另作答为N。[PI 裁定 1b.4]</t>
+          <t>无。冻结表1b.1反向问法记PN（个体在分配前已按既有班级成建制识别），等价于官方1b.1为Y/PY，按须知§三"分配前已完成个体识别／招募→低风险"；1b.4另作答为N。[裁定记录 1b.4]</t>
         </is>
       </c>
       <c r="T12" s="5" t="inlineStr"/>
@@ -2151,7 +2151,7 @@
       <c r="R13" s="5" t="inlineStr"/>
       <c r="S13" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.1]</t>
+          <t>[裁定记录 2.1]</t>
         </is>
       </c>
       <c r="T13" s="5" t="inlineStr"/>
@@ -2351,7 +2351,7 @@
       <c r="R15" s="5" t="inlineStr"/>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.3]</t>
+          <t>[裁定记录 2.3]</t>
         </is>
       </c>
       <c r="T15" s="5" t="inlineStr"/>
@@ -2649,7 +2649,7 @@
       <c r="R18" s="5" t="inlineStr"/>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.6]</t>
+          <t>[裁定记录 2.6]</t>
         </is>
       </c>
       <c r="T18" s="5" t="inlineStr"/>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="S19" s="5" t="inlineStr">
         <is>
-          <t>无（说明见下方"编码说明"第2条：须知§三域2行未覆盖"2.6=N/PN且2.7=N/PN"组合，本行按官方域2算法——分析不适当而影响非实质→有一些疑虑——推导，算法建议与最终判断一致，未偏离）。[PI 裁定 2.7]</t>
+          <t>无（说明见下方"编码说明"第2条：须知§三域2行未覆盖"2.6=N/PN且2.7=N/PN"组合，本行按官方域2算法——分析不适当而影响非实质→有一些疑虑——推导，算法建议与最终判断一致，未偏离）。[裁定记录 2.7]</t>
         </is>
       </c>
       <c r="T19" s="5" t="inlineStr"/>
@@ -3265,7 +3265,7 @@
       <c r="R24" s="5" t="inlineStr"/>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.1]</t>
+          <t>[裁定记录 4.1]</t>
         </is>
       </c>
       <c r="T24" s="5" t="inlineStr"/>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="S31" s="5" t="inlineStr">
         <is>
-          <t>无。5.1=NI且5.2、5.3均为PN，按须知§三"5.1非Y/PY而5.2、5.3均N/PN→有一些疑虑"。[PI 裁定 5.3]</t>
+          <t>无。5.1=NI且5.2、5.3均为PN，按须知§三"5.1非Y/PY而5.2、5.3均N/PN→有一些疑虑"。[裁定记录 5.3]</t>
         </is>
       </c>
       <c r="T31" s="5" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="S38" s="5" t="inlineStr">
         <is>
-          <t>无。1b.1（反向问法）记PN，等价于官方1b.1为Y/PY；1b.4=N。[PI 裁定 1b.4]</t>
+          <t>无。1b.1（反向问法）记PN，等价于官方1b.1为Y/PY；1b.4=N。[裁定记录 1b.4]</t>
         </is>
       </c>
       <c r="T38" s="5" t="inlineStr"/>
@@ -4799,7 +4799,7 @@
       <c r="R39" s="5" t="inlineStr"/>
       <c r="S39" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.1]</t>
+          <t>[裁定记录 2.1]</t>
         </is>
       </c>
       <c r="T39" s="5" t="inlineStr"/>
@@ -4999,7 +4999,7 @@
       <c r="R41" s="5" t="inlineStr"/>
       <c r="S41" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.3]</t>
+          <t>[裁定记录 2.3]</t>
         </is>
       </c>
       <c r="T41" s="5" t="inlineStr"/>
@@ -5297,7 +5297,7 @@
       <c r="R44" s="5" t="inlineStr"/>
       <c r="S44" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.6]</t>
+          <t>[裁定记录 2.6]</t>
         </is>
       </c>
       <c r="T44" s="5" t="inlineStr"/>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="S45" s="5" t="inlineStr">
         <is>
-          <t>无（组合未见于须知§三域2行，按官方域2算法推导；说明同"编码说明"第2条）。[PI 裁定 2.7]</t>
+          <t>无（组合未见于须知§三域2行，按官方域2算法推导；说明同"编码说明"第2条）。[裁定记录 2.7]</t>
         </is>
       </c>
       <c r="T45" s="5" t="inlineStr"/>
@@ -5913,7 +5913,7 @@
       <c r="R50" s="5" t="inlineStr"/>
       <c r="S50" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.1]</t>
+          <t>[裁定记录 4.1]</t>
         </is>
       </c>
       <c r="T50" s="5" t="inlineStr"/>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="S57" s="5" t="inlineStr">
         <is>
-          <t>无。5.1=NI、5.2与5.3均PN。[PI 裁定 5.3]</t>
+          <t>无。5.1=NI、5.2与5.3均PN。[裁定记录 5.3]</t>
         </is>
       </c>
       <c r="T57" s="5" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="S64" s="5" t="inlineStr">
         <is>
-          <t>无。1b.1（反向问法）记PN，等价于官方1b.1为Y/PY；1b.4=N。[PI 裁定 1b.4]</t>
+          <t>无。1b.1（反向问法）记PN，等价于官方1b.1为Y/PY；1b.4=N。[裁定记录 1b.4]</t>
         </is>
       </c>
       <c r="T64" s="5" t="inlineStr"/>
@@ -7447,7 +7447,7 @@
       <c r="R65" s="5" t="inlineStr"/>
       <c r="S65" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.1]</t>
+          <t>[裁定记录 2.1]</t>
         </is>
       </c>
       <c r="T65" s="5" t="inlineStr"/>
@@ -7647,7 +7647,7 @@
       <c r="R67" s="5" t="inlineStr"/>
       <c r="S67" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.3]</t>
+          <t>[裁定记录 2.3]</t>
         </is>
       </c>
       <c r="T67" s="5" t="inlineStr"/>
@@ -7945,7 +7945,7 @@
       <c r="R70" s="5" t="inlineStr"/>
       <c r="S70" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.6]</t>
+          <t>[裁定记录 2.6]</t>
         </is>
       </c>
       <c r="T70" s="5" t="inlineStr"/>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="S71" s="5" t="inlineStr">
         <is>
-          <t>无（组合未见于须知§三域2行，按官方域2算法推导；说明同"编码说明"第2条）。[PI 裁定 2.7]</t>
+          <t>无（组合未见于须知§三域2行，按官方域2算法推导；说明同"编码说明"第2条）。[裁定记录 2.7]</t>
         </is>
       </c>
       <c r="T71" s="5" t="inlineStr"/>
@@ -8561,7 +8561,7 @@
       <c r="R76" s="5" t="inlineStr"/>
       <c r="S76" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.1]</t>
+          <t>[裁定记录 4.1]</t>
         </is>
       </c>
       <c r="T76" s="5" t="inlineStr"/>
@@ -8663,7 +8663,7 @@
       <c r="R77" s="5" t="inlineStr"/>
       <c r="S77" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.2]</t>
+          <t>[裁定记录 4.2]</t>
         </is>
       </c>
       <c r="T77" s="5" t="inlineStr"/>
@@ -8765,7 +8765,7 @@
       <c r="R78" s="5" t="inlineStr"/>
       <c r="S78" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.3]</t>
+          <t>[裁定记录 4.3]</t>
         </is>
       </c>
       <c r="T78" s="5" t="inlineStr"/>
@@ -8867,7 +8867,7 @@
       <c r="R79" s="5" t="inlineStr"/>
       <c r="S79" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.4]</t>
+          <t>[裁定记录 4.4]</t>
         </is>
       </c>
       <c r="T79" s="5" t="inlineStr"/>
@@ -8977,7 +8977,7 @@
       </c>
       <c r="S80" s="5" t="inlineStr">
         <is>
-          <t>无。4.3=NI（无从判断评价者是否知晓）→按须知§三"无从判断是否受影响→有一些疑虑"；4.4=PY、4.5=PN为逐层记录。[PI 裁定 4.5]</t>
+          <t>无。4.3=NI（无从判断评价者是否知晓）→按须知§三"无从判断是否受影响→有一些疑虑"；4.4=PY、4.5=PN为逐层记录。[裁定记录 4.5]</t>
         </is>
       </c>
       <c r="T80" s="5" t="inlineStr"/>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="S83" s="5" t="inlineStr">
         <is>
-          <t>无。5.1=NI且5.2、5.3均为PN。[PI 裁定 5.3]</t>
+          <t>无。5.1=NI且5.2、5.3均为PN。[裁定记录 5.3]</t>
         </is>
       </c>
       <c r="T83" s="5" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="S90" s="5" t="inlineStr">
         <is>
-          <t>无。1b.1（反向问法）记PN，1b.4=N。[PI 裁定 1b.4]</t>
+          <t>无。1b.1（反向问法）记PN，1b.4=N。[裁定记录 1b.4]</t>
         </is>
       </c>
       <c r="T90" s="5" t="inlineStr"/>
@@ -10107,7 +10107,7 @@
       <c r="R91" s="5" t="inlineStr"/>
       <c r="S91" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.1]</t>
+          <t>[裁定记录 2.1]</t>
         </is>
       </c>
       <c r="T91" s="5" t="inlineStr"/>
@@ -10307,7 +10307,7 @@
       <c r="R93" s="5" t="inlineStr"/>
       <c r="S93" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.3]</t>
+          <t>[裁定记录 2.3]</t>
         </is>
       </c>
       <c r="T93" s="5" t="inlineStr"/>
@@ -10605,7 +10605,7 @@
       <c r="R96" s="5" t="inlineStr"/>
       <c r="S96" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.6]</t>
+          <t>[裁定记录 2.6]</t>
         </is>
       </c>
       <c r="T96" s="5" t="inlineStr"/>
@@ -10715,7 +10715,7 @@
       </c>
       <c r="S97" s="5" t="inlineStr">
         <is>
-          <t>无（组合未见于须知§三域2行，按官方域2算法推导；说明同"编码说明"第2条）。[PI 裁定 2.7]</t>
+          <t>无（组合未见于须知§三域2行，按官方域2算法推导；说明同"编码说明"第2条）。[裁定记录 2.7]</t>
         </is>
       </c>
       <c r="T97" s="5" t="inlineStr"/>
@@ -11221,7 +11221,7 @@
       <c r="R102" s="5" t="inlineStr"/>
       <c r="S102" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.1]</t>
+          <t>[裁定记录 4.1]</t>
         </is>
       </c>
       <c r="T102" s="5" t="inlineStr"/>
@@ -11323,7 +11323,7 @@
       <c r="R103" s="5" t="inlineStr"/>
       <c r="S103" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.2]</t>
+          <t>[裁定记录 4.2]</t>
         </is>
       </c>
       <c r="T103" s="5" t="inlineStr"/>
@@ -11425,7 +11425,7 @@
       <c r="R104" s="5" t="inlineStr"/>
       <c r="S104" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.3]</t>
+          <t>[裁定记录 4.3]</t>
         </is>
       </c>
       <c r="T104" s="5" t="inlineStr"/>
@@ -11527,7 +11527,7 @@
       <c r="R105" s="5" t="inlineStr"/>
       <c r="S105" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.4]</t>
+          <t>[裁定记录 4.4]</t>
         </is>
       </c>
       <c r="T105" s="5" t="inlineStr"/>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="S106" s="5" t="inlineStr">
         <is>
-          <t>无。4.3=NI→"无从判断是否受影响→有一些疑虑"；4.4=PY、4.5=PN为逐层记录。[PI 裁定 4.5]</t>
+          <t>无。4.3=NI→"无从判断是否受影响→有一些疑虑"；4.4=PY、4.5=PN为逐层记录。[裁定记录 4.5]</t>
         </is>
       </c>
       <c r="T106" s="5" t="inlineStr"/>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="S109" s="5" t="inlineStr">
         <is>
-          <t>无。5.1=NI且5.2、5.3均为PN。[PI 裁定 5.3]</t>
+          <t>无。5.1=NI且5.2、5.3均为PN。[裁定记录 5.3]</t>
         </is>
       </c>
       <c r="T109" s="5" t="inlineStr">
@@ -12053,7 +12053,7 @@
       <c r="R110" s="5" t="inlineStr"/>
       <c r="S110" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 1.1]</t>
+          <t>[裁定记录 1.1]</t>
         </is>
       </c>
       <c r="T110" s="5" t="inlineStr"/>
@@ -12363,7 +12363,7 @@
       <c r="R113" s="5" t="inlineStr"/>
       <c r="S113" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.1]</t>
+          <t>[裁定记录 2.1]</t>
         </is>
       </c>
       <c r="T113" s="5" t="inlineStr"/>
@@ -12465,7 +12465,7 @@
       <c r="R114" s="5" t="inlineStr"/>
       <c r="S114" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.2]</t>
+          <t>[裁定记录 2.2]</t>
         </is>
       </c>
       <c r="T114" s="5" t="inlineStr"/>
@@ -12567,7 +12567,7 @@
       <c r="R115" s="5" t="inlineStr"/>
       <c r="S115" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.3]</t>
+          <t>[裁定记录 2.3]</t>
         </is>
       </c>
       <c r="T115" s="5" t="inlineStr"/>
@@ -12865,7 +12865,7 @@
       <c r="R118" s="5" t="inlineStr"/>
       <c r="S118" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.6]</t>
+          <t>[裁定记录 2.6]</t>
         </is>
       </c>
       <c r="T118" s="5" t="inlineStr"/>
@@ -12975,7 +12975,7 @@
       </c>
       <c r="S119" s="5" t="inlineStr">
         <is>
-          <t>—[PI 裁定 2.7]</t>
+          <t>—[裁定记录 2.7]</t>
         </is>
       </c>
       <c r="T119" s="5" t="inlineStr"/>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="S123" s="5" t="inlineStr">
         <is>
-          <t>—[PI 裁定 3.4]</t>
+          <t>—[裁定记录 3.4]</t>
         </is>
       </c>
       <c r="T123" s="5" t="inlineStr"/>
@@ -13677,7 +13677,7 @@
       <c r="R126" s="5" t="inlineStr"/>
       <c r="S126" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.3]</t>
+          <t>[裁定记录 4.3]</t>
         </is>
       </c>
       <c r="T126" s="5" t="inlineStr"/>
@@ -13779,7 +13779,7 @@
       <c r="R127" s="5" t="inlineStr"/>
       <c r="S127" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.4]</t>
+          <t>[裁定记录 4.4]</t>
         </is>
       </c>
       <c r="T127" s="5" t="inlineStr"/>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="S128" s="5" t="inlineStr">
         <is>
-          <t>—[PI 裁定 4.5]</t>
+          <t>—[裁定记录 4.5]</t>
         </is>
       </c>
       <c r="T128" s="5" t="inlineStr"/>
@@ -13991,7 +13991,7 @@
       <c r="R129" s="5" t="inlineStr"/>
       <c r="S129" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.1]</t>
+          <t>[裁定记录 5.1]</t>
         </is>
       </c>
       <c r="T129" s="5" t="inlineStr"/>
@@ -14309,7 +14309,7 @@
       <c r="R132" s="5" t="inlineStr"/>
       <c r="S132" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 1.1]</t>
+          <t>[裁定记录 1.1]</t>
         </is>
       </c>
       <c r="T132" s="5" t="inlineStr"/>
@@ -15023,7 +15023,7 @@
       <c r="R139" s="5" t="inlineStr"/>
       <c r="S139" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.1]</t>
+          <t>[裁定记录 2.1]</t>
         </is>
       </c>
       <c r="T139" s="5" t="inlineStr"/>
@@ -15125,7 +15125,7 @@
       <c r="R140" s="5" t="inlineStr"/>
       <c r="S140" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.2]</t>
+          <t>[裁定记录 2.2]</t>
         </is>
       </c>
       <c r="T140" s="5" t="inlineStr"/>
@@ -15227,7 +15227,7 @@
       <c r="R141" s="5" t="inlineStr"/>
       <c r="S141" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.3]</t>
+          <t>[裁定记录 2.3]</t>
         </is>
       </c>
       <c r="T141" s="5" t="inlineStr"/>
@@ -15525,7 +15525,7 @@
       <c r="R144" s="5" t="inlineStr"/>
       <c r="S144" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.6]</t>
+          <t>[裁定记录 2.6]</t>
         </is>
       </c>
       <c r="T144" s="5" t="inlineStr"/>
@@ -15635,7 +15635,7 @@
       </c>
       <c r="S145" s="5" t="inlineStr">
         <is>
-          <t>—[PI 裁定 2.7]</t>
+          <t>—[裁定记录 2.7]</t>
         </is>
       </c>
       <c r="T145" s="5" t="inlineStr"/>
@@ -16141,7 +16141,7 @@
       <c r="R150" s="5" t="inlineStr"/>
       <c r="S150" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.1]</t>
+          <t>[裁定记录 4.1]</t>
         </is>
       </c>
       <c r="T150" s="5" t="inlineStr"/>
@@ -16341,7 +16341,7 @@
       <c r="R152" s="5" t="inlineStr"/>
       <c r="S152" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.3]</t>
+          <t>[裁定记录 4.3]</t>
         </is>
       </c>
       <c r="T152" s="5" t="inlineStr"/>
@@ -16549,7 +16549,7 @@
       </c>
       <c r="S154" s="5" t="inlineStr">
         <is>
-          <t>—[PI 裁定 4.5]</t>
+          <t>—[裁定记录 4.5]</t>
         </is>
       </c>
       <c r="T154" s="5" t="inlineStr"/>
@@ -16651,7 +16651,7 @@
       <c r="R155" s="5" t="inlineStr"/>
       <c r="S155" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.1]</t>
+          <t>[裁定记录 5.1]</t>
         </is>
       </c>
       <c r="T155" s="5" t="inlineStr"/>
@@ -16969,7 +16969,7 @@
       <c r="R158" s="5" t="inlineStr"/>
       <c r="S158" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 1.1]</t>
+          <t>[裁定记录 1.1]</t>
         </is>
       </c>
       <c r="T158" s="5" t="inlineStr"/>
@@ -17683,7 +17683,7 @@
       <c r="R165" s="5" t="inlineStr"/>
       <c r="S165" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.1]</t>
+          <t>[裁定记录 2.1]</t>
         </is>
       </c>
       <c r="T165" s="5" t="inlineStr"/>
@@ -17785,7 +17785,7 @@
       <c r="R166" s="5" t="inlineStr"/>
       <c r="S166" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.2]</t>
+          <t>[裁定记录 2.2]</t>
         </is>
       </c>
       <c r="T166" s="5" t="inlineStr"/>
@@ -17887,7 +17887,7 @@
       <c r="R167" s="5" t="inlineStr"/>
       <c r="S167" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.3]</t>
+          <t>[裁定记录 2.3]</t>
         </is>
       </c>
       <c r="T167" s="5" t="inlineStr"/>
@@ -18185,7 +18185,7 @@
       <c r="R170" s="5" t="inlineStr"/>
       <c r="S170" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.6]</t>
+          <t>[裁定记录 2.6]</t>
         </is>
       </c>
       <c r="T170" s="5" t="inlineStr"/>
@@ -18295,7 +18295,7 @@
       </c>
       <c r="S171" s="5" t="inlineStr">
         <is>
-          <t>—[PI 裁定 2.7]</t>
+          <t>—[裁定记录 2.7]</t>
         </is>
       </c>
       <c r="T171" s="5" t="inlineStr"/>
@@ -18801,7 +18801,7 @@
       <c r="R176" s="5" t="inlineStr"/>
       <c r="S176" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.1]</t>
+          <t>[裁定记录 4.1]</t>
         </is>
       </c>
       <c r="T176" s="5" t="inlineStr"/>
@@ -19001,7 +19001,7 @@
       <c r="R178" s="5" t="inlineStr"/>
       <c r="S178" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.3]</t>
+          <t>[裁定记录 4.3]</t>
         </is>
       </c>
       <c r="T178" s="5" t="inlineStr"/>
@@ -19209,7 +19209,7 @@
       </c>
       <c r="S180" s="5" t="inlineStr">
         <is>
-          <t>—[PI 裁定 4.5]</t>
+          <t>—[裁定记录 4.5]</t>
         </is>
       </c>
       <c r="T180" s="5" t="inlineStr"/>
@@ -19311,7 +19311,7 @@
       <c r="R181" s="5" t="inlineStr"/>
       <c r="S181" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.1]</t>
+          <t>[裁定记录 5.1]</t>
         </is>
       </c>
       <c r="T181" s="5" t="inlineStr"/>
@@ -19629,7 +19629,7 @@
       <c r="R184" s="5" t="inlineStr"/>
       <c r="S184" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 1.1]</t>
+          <t>[裁定记录 1.1]</t>
         </is>
       </c>
       <c r="T184" s="5" t="inlineStr"/>
@@ -20343,7 +20343,7 @@
       <c r="R191" s="5" t="inlineStr"/>
       <c r="S191" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.1]</t>
+          <t>[裁定记录 2.1]</t>
         </is>
       </c>
       <c r="T191" s="5" t="inlineStr"/>
@@ -20445,7 +20445,7 @@
       <c r="R192" s="5" t="inlineStr"/>
       <c r="S192" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.2]</t>
+          <t>[裁定记录 2.2]</t>
         </is>
       </c>
       <c r="T192" s="5" t="inlineStr"/>
@@ -20547,7 +20547,7 @@
       <c r="R193" s="5" t="inlineStr"/>
       <c r="S193" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.3]</t>
+          <t>[裁定记录 2.3]</t>
         </is>
       </c>
       <c r="T193" s="5" t="inlineStr"/>
@@ -20845,7 +20845,7 @@
       <c r="R196" s="5" t="inlineStr"/>
       <c r="S196" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.6]</t>
+          <t>[裁定记录 2.6]</t>
         </is>
       </c>
       <c r="T196" s="5" t="inlineStr"/>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="S197" s="5" t="inlineStr">
         <is>
-          <t>—[PI 裁定 2.7]</t>
+          <t>—[裁定记录 2.7]</t>
         </is>
       </c>
       <c r="T197" s="5" t="inlineStr"/>
@@ -21359,7 +21359,7 @@
       </c>
       <c r="S201" s="5" t="inlineStr">
         <is>
-          <t>—[PI 裁定 3.4]</t>
+          <t>—[裁定记录 3.4]</t>
         </is>
       </c>
       <c r="T201" s="5" t="inlineStr"/>
@@ -21657,7 +21657,7 @@
       <c r="R204" s="5" t="inlineStr"/>
       <c r="S204" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.3]</t>
+          <t>[裁定记录 4.3]</t>
         </is>
       </c>
       <c r="T204" s="5" t="inlineStr"/>
@@ -21759,7 +21759,7 @@
       <c r="R205" s="5" t="inlineStr"/>
       <c r="S205" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.4]</t>
+          <t>[裁定记录 4.4]</t>
         </is>
       </c>
       <c r="T205" s="5" t="inlineStr"/>
@@ -21869,7 +21869,7 @@
       </c>
       <c r="S206" s="5" t="inlineStr">
         <is>
-          <t>—[PI 裁定 4.5]</t>
+          <t>—[裁定记录 4.5]</t>
         </is>
       </c>
       <c r="T206" s="5" t="inlineStr"/>
@@ -21971,7 +21971,7 @@
       <c r="R207" s="5" t="inlineStr"/>
       <c r="S207" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.1]</t>
+          <t>[裁定记录 5.1]</t>
         </is>
       </c>
       <c r="T207" s="5" t="inlineStr"/>
@@ -22289,7 +22289,7 @@
       <c r="R210" s="5" t="inlineStr"/>
       <c r="S210" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 1.1]</t>
+          <t>[裁定记录 1.1]</t>
         </is>
       </c>
       <c r="T210" s="5" t="inlineStr"/>
@@ -23003,7 +23003,7 @@
       <c r="R217" s="5" t="inlineStr"/>
       <c r="S217" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.1]</t>
+          <t>[裁定记录 2.1]</t>
         </is>
       </c>
       <c r="T217" s="5" t="inlineStr"/>
@@ -23105,7 +23105,7 @@
       <c r="R218" s="5" t="inlineStr"/>
       <c r="S218" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.2]</t>
+          <t>[裁定记录 2.2]</t>
         </is>
       </c>
       <c r="T218" s="5" t="inlineStr"/>
@@ -23207,7 +23207,7 @@
       <c r="R219" s="5" t="inlineStr"/>
       <c r="S219" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.3]</t>
+          <t>[裁定记录 2.3]</t>
         </is>
       </c>
       <c r="T219" s="5" t="inlineStr"/>
@@ -23505,7 +23505,7 @@
       <c r="R222" s="5" t="inlineStr"/>
       <c r="S222" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.6]</t>
+          <t>[裁定记录 2.6]</t>
         </is>
       </c>
       <c r="T222" s="5" t="inlineStr"/>
@@ -23615,7 +23615,7 @@
       </c>
       <c r="S223" s="5" t="inlineStr">
         <is>
-          <t>—[PI 裁定 2.7]</t>
+          <t>—[裁定记录 2.7]</t>
         </is>
       </c>
       <c r="T223" s="5" t="inlineStr"/>
@@ -24019,7 +24019,7 @@
       </c>
       <c r="S227" s="5" t="inlineStr">
         <is>
-          <t>—[PI 裁定 3.4]</t>
+          <t>—[裁定记录 3.4]</t>
         </is>
       </c>
       <c r="T227" s="5" t="inlineStr"/>
@@ -24317,7 +24317,7 @@
       <c r="R230" s="5" t="inlineStr"/>
       <c r="S230" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.3]</t>
+          <t>[裁定记录 4.3]</t>
         </is>
       </c>
       <c r="T230" s="5" t="inlineStr"/>
@@ -24419,7 +24419,7 @@
       <c r="R231" s="5" t="inlineStr"/>
       <c r="S231" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.4]</t>
+          <t>[裁定记录 4.4]</t>
         </is>
       </c>
       <c r="T231" s="5" t="inlineStr"/>
@@ -24529,7 +24529,7 @@
       </c>
       <c r="S232" s="5" t="inlineStr">
         <is>
-          <t>—[PI 裁定 4.5]</t>
+          <t>—[裁定记录 4.5]</t>
         </is>
       </c>
       <c r="T232" s="5" t="inlineStr"/>
@@ -24631,7 +24631,7 @@
       <c r="R233" s="5" t="inlineStr"/>
       <c r="S233" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.1]</t>
+          <t>[裁定记录 5.1]</t>
         </is>
       </c>
       <c r="T233" s="5" t="inlineStr"/>
@@ -25047,7 +25047,7 @@
       <c r="R237" s="5" t="inlineStr"/>
       <c r="S237" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 1.2]</t>
+          <t>[裁定记录 1.2]</t>
         </is>
       </c>
       <c r="T237" s="5" t="inlineStr"/>
@@ -25549,7 +25549,7 @@
       <c r="R242" s="5" t="inlineStr"/>
       <c r="S242" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.1]</t>
+          <t>[裁定记录 2.1]</t>
         </is>
       </c>
       <c r="T242" s="5" t="inlineStr"/>
@@ -25651,7 +25651,7 @@
       <c r="R243" s="5" t="inlineStr"/>
       <c r="S243" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.2]</t>
+          <t>[裁定记录 2.2]</t>
         </is>
       </c>
       <c r="T243" s="5" t="inlineStr"/>
@@ -26161,7 +26161,7 @@
       </c>
       <c r="S248" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 3.3]</t>
+          <t>[裁定记录 3.3]</t>
         </is>
       </c>
       <c r="T248" s="5" t="inlineStr"/>
@@ -26957,7 +26957,7 @@
       <c r="R256" s="5" t="inlineStr"/>
       <c r="S256" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.1]</t>
+          <t>[裁定记录 5.1]</t>
         </is>
       </c>
       <c r="T256" s="5" t="inlineStr"/>
@@ -27059,7 +27059,7 @@
       <c r="R257" s="5" t="inlineStr"/>
       <c r="S257" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.2]</t>
+          <t>[裁定记录 5.2]</t>
         </is>
       </c>
       <c r="T257" s="5" t="inlineStr"/>
@@ -27161,7 +27161,7 @@
       <c r="R258" s="5" t="inlineStr"/>
       <c r="S258" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.3]</t>
+          <t>[裁定记录 5.3]</t>
         </is>
       </c>
       <c r="T258" s="5" t="inlineStr"/>
@@ -27263,7 +27263,7 @@
       <c r="R259" s="5" t="inlineStr"/>
       <c r="S259" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.4]</t>
+          <t>[裁定记录 5.4]</t>
         </is>
       </c>
       <c r="T259" s="5" t="inlineStr"/>
@@ -27365,7 +27365,7 @@
       <c r="R260" s="5" t="inlineStr"/>
       <c r="S260" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.5]</t>
+          <t>[裁定记录 5.5]</t>
         </is>
       </c>
       <c r="T260" s="5" t="inlineStr"/>
@@ -27467,7 +27467,7 @@
       <c r="R261" s="5" t="inlineStr"/>
       <c r="S261" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.6]</t>
+          <t>[裁定记录 5.6]</t>
         </is>
       </c>
       <c r="T261" s="5" t="inlineStr"/>
@@ -27577,7 +27577,7 @@
       </c>
       <c r="S262" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.7]</t>
+          <t>[裁定记录 5.7]</t>
         </is>
       </c>
       <c r="T262" s="5" t="inlineStr"/>
@@ -27679,7 +27679,7 @@
       <c r="R263" s="5" t="inlineStr"/>
       <c r="S263" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 6.1]</t>
+          <t>[裁定记录 6.1]</t>
         </is>
       </c>
       <c r="T263" s="5" t="inlineStr"/>
@@ -28083,7 +28083,7 @@
       <c r="R267" s="5" t="inlineStr"/>
       <c r="S267" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 7.1]</t>
+          <t>[裁定记录 7.1]</t>
         </is>
       </c>
       <c r="T267" s="5" t="inlineStr"/>
@@ -28703,7 +28703,7 @@
       <c r="R273" s="5" t="inlineStr"/>
       <c r="S273" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 1b.1]</t>
+          <t>[裁定记录 1b.1]</t>
         </is>
       </c>
       <c r="T273" s="5" t="inlineStr"/>
@@ -29009,7 +29009,7 @@
       </c>
       <c r="S276" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 1b.4]</t>
+          <t>[裁定记录 1b.4]</t>
         </is>
       </c>
       <c r="T276" s="5" t="inlineStr"/>
@@ -29707,7 +29707,7 @@
       </c>
       <c r="S283" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.7]</t>
+          <t>[裁定记录 2.7]</t>
         </is>
       </c>
       <c r="T283" s="5" t="inlineStr"/>
@@ -29809,7 +29809,7 @@
       <c r="R284" s="5" t="inlineStr"/>
       <c r="S284" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 3.1]</t>
+          <t>[裁定记录 3.1]</t>
         </is>
       </c>
       <c r="T284" s="5" t="inlineStr"/>
@@ -30213,7 +30213,7 @@
       <c r="R288" s="5" t="inlineStr"/>
       <c r="S288" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.1]</t>
+          <t>[裁定记录 4.1]</t>
         </is>
       </c>
       <c r="T288" s="5" t="inlineStr"/>
@@ -30413,7 +30413,7 @@
       <c r="R290" s="5" t="inlineStr"/>
       <c r="S290" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.3]</t>
+          <t>[裁定记录 4.3]</t>
         </is>
       </c>
       <c r="T290" s="5" t="inlineStr"/>
@@ -30515,7 +30515,7 @@
       <c r="R291" s="5" t="inlineStr"/>
       <c r="S291" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.4]</t>
+          <t>[裁定记录 4.4]</t>
         </is>
       </c>
       <c r="T291" s="5" t="inlineStr"/>
@@ -30625,7 +30625,7 @@
       </c>
       <c r="S292" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.5]</t>
+          <t>[裁定记录 4.5]</t>
         </is>
       </c>
       <c r="T292" s="5" t="inlineStr"/>
@@ -30727,7 +30727,7 @@
       <c r="R293" s="5" t="inlineStr"/>
       <c r="S293" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.1]</t>
+          <t>[裁定记录 5.1]</t>
         </is>
       </c>
       <c r="T293" s="5" t="inlineStr"/>
@@ -30829,7 +30829,7 @@
       <c r="R294" s="5" t="inlineStr"/>
       <c r="S294" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.2]</t>
+          <t>[裁定记录 5.2]</t>
         </is>
       </c>
       <c r="T294" s="5" t="inlineStr"/>
@@ -30939,7 +30939,7 @@
       </c>
       <c r="S295" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.3]</t>
+          <t>[裁定记录 5.3]</t>
         </is>
       </c>
       <c r="T295" s="5" t="inlineStr">
@@ -31257,7 +31257,7 @@
       </c>
       <c r="S298" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 1.3]</t>
+          <t>[裁定记录 1.3]</t>
         </is>
       </c>
       <c r="T298" s="5" t="inlineStr"/>
@@ -31359,7 +31359,7 @@
       <c r="R299" s="5" t="inlineStr"/>
       <c r="S299" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 1b.1]</t>
+          <t>[裁定记录 1b.1]</t>
         </is>
       </c>
       <c r="T299" s="5" t="inlineStr"/>
@@ -31665,7 +31665,7 @@
       </c>
       <c r="S302" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 1b.4]</t>
+          <t>[裁定记录 1b.4]</t>
         </is>
       </c>
       <c r="T302" s="5" t="inlineStr"/>
@@ -32363,7 +32363,7 @@
       </c>
       <c r="S309" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 2.7]</t>
+          <t>[裁定记录 2.7]</t>
         </is>
       </c>
       <c r="T309" s="5" t="inlineStr"/>
@@ -32465,7 +32465,7 @@
       <c r="R310" s="5" t="inlineStr"/>
       <c r="S310" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 3.1]</t>
+          <t>[裁定记录 3.1]</t>
         </is>
       </c>
       <c r="T310" s="5" t="inlineStr"/>
@@ -32869,7 +32869,7 @@
       <c r="R314" s="5" t="inlineStr"/>
       <c r="S314" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.1]</t>
+          <t>[裁定记录 4.1]</t>
         </is>
       </c>
       <c r="T314" s="5" t="inlineStr"/>
@@ -33069,7 +33069,7 @@
       <c r="R316" s="5" t="inlineStr"/>
       <c r="S316" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.3]</t>
+          <t>[裁定记录 4.3]</t>
         </is>
       </c>
       <c r="T316" s="5" t="inlineStr"/>
@@ -33171,7 +33171,7 @@
       <c r="R317" s="5" t="inlineStr"/>
       <c r="S317" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.4]</t>
+          <t>[裁定记录 4.4]</t>
         </is>
       </c>
       <c r="T317" s="5" t="inlineStr"/>
@@ -33281,7 +33281,7 @@
       </c>
       <c r="S318" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 4.5]</t>
+          <t>[裁定记录 4.5]</t>
         </is>
       </c>
       <c r="T318" s="5" t="inlineStr"/>
@@ -33383,7 +33383,7 @@
       <c r="R319" s="5" t="inlineStr"/>
       <c r="S319" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.1]</t>
+          <t>[裁定记录 5.1]</t>
         </is>
       </c>
       <c r="T319" s="5" t="inlineStr"/>
@@ -33485,7 +33485,7 @@
       <c r="R320" s="5" t="inlineStr"/>
       <c r="S320" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.2]</t>
+          <t>[裁定记录 5.2]</t>
         </is>
       </c>
       <c r="T320" s="5" t="inlineStr"/>
@@ -33595,7 +33595,7 @@
       </c>
       <c r="S321" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 5.3]</t>
+          <t>[裁定记录 5.3]</t>
         </is>
       </c>
       <c r="T321" s="5" t="inlineStr">
@@ -33803,7 +33803,7 @@
       <c r="R323" s="5" t="inlineStr"/>
       <c r="S323" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 1.2]</t>
+          <t>[裁定记录 X 系列 1.2]</t>
         </is>
       </c>
       <c r="T323" s="5" t="inlineStr"/>
@@ -33905,7 +33905,7 @@
       <c r="R324" s="5" t="inlineStr"/>
       <c r="S324" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 1.3]</t>
+          <t>[裁定记录 X 系列 1.3]</t>
         </is>
       </c>
       <c r="T324" s="5" t="inlineStr"/>
@@ -34105,7 +34105,7 @@
       <c r="R326" s="5" t="inlineStr"/>
       <c r="S326" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 1.5]</t>
+          <t>[裁定记录 X 系列 1.5]</t>
         </is>
       </c>
       <c r="T326" s="5" t="inlineStr"/>
@@ -34313,7 +34313,7 @@
       <c r="R328" s="5" t="inlineStr"/>
       <c r="S328" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 2.1]</t>
+          <t>[裁定记录 X 系列 2.1]</t>
         </is>
       </c>
       <c r="T328" s="5" t="inlineStr"/>
@@ -34415,7 +34415,7 @@
       <c r="R329" s="5" t="inlineStr"/>
       <c r="S329" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 2.2]</t>
+          <t>[裁定记录 X 系列 2.2]</t>
         </is>
       </c>
       <c r="T329" s="5" t="inlineStr"/>
@@ -34925,7 +34925,7 @@
       </c>
       <c r="S334" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 3.3]</t>
+          <t>[裁定记录 X 系列 3.3]</t>
         </is>
       </c>
       <c r="T334" s="5" t="inlineStr"/>
@@ -35027,7 +35027,7 @@
       <c r="R335" s="5" t="inlineStr"/>
       <c r="S335" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 4.1]</t>
+          <t>[裁定记录 X 系列 4.1]</t>
         </is>
       </c>
       <c r="T335" s="5" t="inlineStr"/>
@@ -35423,7 +35423,7 @@
       <c r="R339" s="5" t="inlineStr"/>
       <c r="S339" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 4.5]</t>
+          <t>[裁定记录 X 系列 4.5]</t>
         </is>
       </c>
       <c r="T339" s="5" t="inlineStr"/>
@@ -35827,7 +35827,7 @@
       <c r="R343" s="5" t="inlineStr"/>
       <c r="S343" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 5.2]</t>
+          <t>[裁定记录 X 系列 5.2]</t>
         </is>
       </c>
       <c r="T343" s="5" t="inlineStr"/>
@@ -35929,7 +35929,7 @@
       <c r="R344" s="5" t="inlineStr"/>
       <c r="S344" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 5.3]</t>
+          <t>[裁定记录 X 系列 5.3]</t>
         </is>
       </c>
       <c r="T344" s="5" t="inlineStr"/>
@@ -36529,7 +36529,7 @@
       <c r="R350" s="5" t="inlineStr"/>
       <c r="S350" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 6.2]</t>
+          <t>[裁定记录 X 系列 6.2]</t>
         </is>
       </c>
       <c r="T350" s="5" t="inlineStr"/>
@@ -36737,7 +36737,7 @@
       </c>
       <c r="S352" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 6.4]</t>
+          <t>[裁定记录 X 系列 6.4]</t>
         </is>
       </c>
       <c r="T352" s="5" t="inlineStr"/>
@@ -37043,7 +37043,7 @@
       </c>
       <c r="S355" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 7.3]</t>
+          <t>[裁定记录 X 系列 7.3]</t>
         </is>
       </c>
       <c r="T355" s="5" t="inlineStr">
@@ -37251,7 +37251,7 @@
       <c r="R357" s="5" t="inlineStr"/>
       <c r="S357" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 1.2]</t>
+          <t>[裁定记录 X 系列 1.2]</t>
         </is>
       </c>
       <c r="T357" s="5" t="inlineStr"/>
@@ -37353,7 +37353,7 @@
       <c r="R358" s="5" t="inlineStr"/>
       <c r="S358" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 1.3]</t>
+          <t>[裁定记录 X 系列 1.3]</t>
         </is>
       </c>
       <c r="T358" s="5" t="inlineStr"/>
@@ -37553,7 +37553,7 @@
       <c r="R360" s="5" t="inlineStr"/>
       <c r="S360" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 1.5]</t>
+          <t>[裁定记录 X 系列 1.5]</t>
         </is>
       </c>
       <c r="T360" s="5" t="inlineStr"/>
@@ -37761,7 +37761,7 @@
       <c r="R362" s="5" t="inlineStr"/>
       <c r="S362" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 2.1]</t>
+          <t>[裁定记录 X 系列 2.1]</t>
         </is>
       </c>
       <c r="T362" s="5" t="inlineStr"/>
@@ -37863,7 +37863,7 @@
       <c r="R363" s="5" t="inlineStr"/>
       <c r="S363" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 2.2]</t>
+          <t>[裁定记录 X 系列 2.2]</t>
         </is>
       </c>
       <c r="T363" s="5" t="inlineStr"/>
@@ -38373,7 +38373,7 @@
       </c>
       <c r="S368" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 3.3]</t>
+          <t>[裁定记录 X 系列 3.3]</t>
         </is>
       </c>
       <c r="T368" s="5" t="inlineStr"/>
@@ -38475,7 +38475,7 @@
       <c r="R369" s="5" t="inlineStr"/>
       <c r="S369" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 4.1]</t>
+          <t>[裁定记录 X 系列 4.1]</t>
         </is>
       </c>
       <c r="T369" s="5" t="inlineStr"/>
@@ -38871,7 +38871,7 @@
       <c r="R373" s="5" t="inlineStr"/>
       <c r="S373" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 4.5]</t>
+          <t>[裁定记录 X 系列 4.5]</t>
         </is>
       </c>
       <c r="T373" s="5" t="inlineStr"/>
@@ -39177,7 +39177,7 @@
       <c r="R376" s="5" t="inlineStr"/>
       <c r="S376" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 5.1]</t>
+          <t>[裁定记录 X 系列 5.1]</t>
         </is>
       </c>
       <c r="T376" s="5" t="inlineStr"/>
@@ -39279,7 +39279,7 @@
       <c r="R377" s="5" t="inlineStr"/>
       <c r="S377" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 5.2]</t>
+          <t>[裁定记录 X 系列 5.2]</t>
         </is>
       </c>
       <c r="T377" s="5" t="inlineStr"/>
@@ -39381,7 +39381,7 @@
       <c r="R378" s="5" t="inlineStr"/>
       <c r="S378" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 5.3]</t>
+          <t>[裁定记录 X 系列 5.3]</t>
         </is>
       </c>
       <c r="T378" s="5" t="inlineStr"/>
@@ -39483,7 +39483,7 @@
       <c r="R379" s="5" t="inlineStr"/>
       <c r="S379" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 5.4]</t>
+          <t>[裁定记录 X 系列 5.4]</t>
         </is>
       </c>
       <c r="T379" s="5" t="inlineStr"/>
@@ -39585,7 +39585,7 @@
       <c r="R380" s="5" t="inlineStr"/>
       <c r="S380" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 5.5]</t>
+          <t>[裁定记录 X 系列 5.5]</t>
         </is>
       </c>
       <c r="T380" s="5" t="inlineStr"/>
@@ -39687,7 +39687,7 @@
       <c r="R381" s="5" t="inlineStr"/>
       <c r="S381" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 5.6]</t>
+          <t>[裁定记录 X 系列 5.6]</t>
         </is>
       </c>
       <c r="T381" s="5" t="inlineStr"/>
@@ -39797,7 +39797,7 @@
       </c>
       <c r="S382" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 5.7]</t>
+          <t>[裁定记录 X 系列 5.7]</t>
         </is>
       </c>
       <c r="T382" s="5" t="inlineStr"/>
@@ -40201,7 +40201,7 @@
       </c>
       <c r="S386" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 6.4]</t>
+          <t>[裁定记录 X 系列 6.4]</t>
         </is>
       </c>
       <c r="T386" s="5" t="inlineStr"/>
@@ -40507,7 +40507,7 @@
       </c>
       <c r="S389" s="5" t="inlineStr">
         <is>
-          <t>[PI 裁定 X 系列 7.3]</t>
+          <t>[裁定记录 X 系列 7.3]</t>
         </is>
       </c>
       <c r="T389" s="5" t="inlineStr">

--- a/4-偏倚风险评价（数据表）.xlsx
+++ b/4-偏倚风险评价（数据表）.xlsx
@@ -1437,7 +1437,7 @@
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr">
         <is>
-          <t>[PI 编码约定 1.1]</t>
+          <t>[编码约定 1.1]</t>
         </is>
       </c>
       <c r="T6" s="5" t="inlineStr"/>
@@ -4085,7 +4085,7 @@
       <c r="R32" s="5" t="inlineStr"/>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>[PI 编码约定 1.1]</t>
+          <t>[编码约定 1.1]</t>
         </is>
       </c>
       <c r="T32" s="5" t="inlineStr"/>
@@ -6733,7 +6733,7 @@
       <c r="R58" s="5" t="inlineStr"/>
       <c r="S58" s="5" t="inlineStr">
         <is>
-          <t>[PI 编码约定 1.1]</t>
+          <t>[编码约定 1.1]</t>
         </is>
       </c>
       <c r="T58" s="5" t="inlineStr"/>
@@ -9393,7 +9393,7 @@
       <c r="R84" s="5" t="inlineStr"/>
       <c r="S84" s="5" t="inlineStr">
         <is>
-          <t>[PI 编码约定 1.1]</t>
+          <t>[编码约定 1.1]</t>
         </is>
       </c>
       <c r="T84" s="5" t="inlineStr"/>
@@ -28397,7 +28397,7 @@
       <c r="R270" s="5" t="inlineStr"/>
       <c r="S270" s="5" t="inlineStr">
         <is>
-          <t>[PI 编码约定 1.1]</t>
+          <t>[编码约定 1.1]</t>
         </is>
       </c>
       <c r="T270" s="5" t="inlineStr"/>
@@ -31049,7 +31049,7 @@
       <c r="R296" s="5" t="inlineStr"/>
       <c r="S296" s="5" t="inlineStr">
         <is>
-          <t>[PI 编码约定 1.1]</t>
+          <t>[编码约定 1.1]</t>
         </is>
       </c>
       <c r="T296" s="5" t="inlineStr"/>
